--- a/rtss-pre1917/src/main/resources/immigration.xlsx
+++ b/rtss-pre1917/src/main/resources/immigration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF90F01-3DD6-4DD6-8337-9C851884C3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319C8045-89C2-47DF-8CC7-2756680B63D1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="3" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -29,9 +29,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,14 +39,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -418,9 +418,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -458,7 +458,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -564,7 +564,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -706,7 +706,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -715,26 +715,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE7EB44-DA37-426E-8733-CEB32776A88C}">
   <dimension ref="A1:CF163"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.26171875" customWidth="1"/>
-    <col min="2" max="2" width="10.68359375" customWidth="1"/>
-    <col min="3" max="3" width="10.15625" customWidth="1"/>
-    <col min="4" max="4" width="9.68359375" customWidth="1"/>
-    <col min="23" max="23" width="10.41796875" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="23" t="s">
         <v>5</v>
@@ -752,7 +752,7 @@
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
@@ -784,7 +784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <f t="shared" ref="A7:A20" si="0">A8-1</f>
         <v>1881</v>
@@ -822,7 +822,7 @@
         <v>48689</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>1882</v>
@@ -860,7 +860,7 @@
         <v>26006</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>1883</v>
@@ -898,7 +898,7 @@
         <v>25477</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>1884</v>
@@ -936,7 +936,7 @@
         <v>26503</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>1885</v>
@@ -974,7 +974,7 @@
         <v>29497</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>1886</v>
@@ -1012,7 +1012,7 @@
         <v>23547</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>1887</v>
@@ -1050,7 +1050,7 @@
         <v>33837</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>1888</v>
@@ -1088,7 +1088,7 @@
         <v>33036</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>1889</v>
@@ -1126,7 +1126,7 @@
         <v>38891</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>1890</v>
@@ -1164,7 +1164,7 @@
         <v>37780</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <f t="shared" si="0"/>
         <v>1891</v>
@@ -1202,7 +1202,7 @@
         <v>41539</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <f t="shared" si="0"/>
         <v>1892</v>
@@ -1240,7 +1240,7 @@
         <v>38125</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>1893</v>
@@ -1278,7 +1278,7 @@
         <v>43936</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>1894</v>
@@ -1316,7 +1316,7 @@
         <v>49688</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <f>A22-1</f>
         <v>1895</v>
@@ -1354,7 +1354,7 @@
         <v>54197</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>1896</v>
       </c>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <f>A22+1</f>
         <v>1897</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <f t="shared" ref="A24:A41" si="12">A23+1</f>
         <v>1898</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <f t="shared" si="12"/>
         <v>1899</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <f t="shared" si="12"/>
         <v>1900</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <f t="shared" si="12"/>
         <v>1901</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <f t="shared" si="12"/>
         <v>1902</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <f t="shared" si="12"/>
         <v>1903</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <f t="shared" si="12"/>
         <v>1904</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <f t="shared" si="12"/>
         <v>1905</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <f t="shared" si="12"/>
         <v>1906</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <f t="shared" si="12"/>
         <v>1907</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <f t="shared" si="12"/>
         <v>1908</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <f t="shared" si="12"/>
         <v>1909</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <f t="shared" si="12"/>
         <v>1910</v>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <f t="shared" si="12"/>
         <v>1911</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <f t="shared" si="12"/>
         <v>1912</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <f t="shared" si="12"/>
         <v>1913</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <f t="shared" si="12"/>
         <v>1914</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <f t="shared" si="12"/>
         <v>1915</v>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>4</v>
       </c>
@@ -2157,7 +2157,7 @@
       <c r="J42" s="4"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>50</v>
       </c>
@@ -2181,7 +2181,7 @@
       <c r="J43" s="4"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>51</v>
       </c>
@@ -2205,36 +2205,36 @@
       <c r="J44" s="4"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>18</v>
       </c>
       <c r="M48" s="6"/>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>60</v>
       </c>
       <c r="M49" s="6"/>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:84" x14ac:dyDescent="0.25">
       <c r="O50" s="1"/>
     </row>
-    <row r="51" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:84" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>7</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>0</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <f t="shared" ref="A53:A66" si="13">A54-1</f>
         <v>1881</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <f t="shared" si="13"/>
         <v>1882</v>
@@ -3133,7 +3133,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="55" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <f t="shared" si="13"/>
         <v>1883</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <f t="shared" si="13"/>
         <v>1884</v>
@@ -3695,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <f t="shared" si="13"/>
         <v>1885</v>
@@ -3976,7 +3976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <f t="shared" si="13"/>
         <v>1886</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <f t="shared" si="13"/>
         <v>1887</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <f t="shared" si="13"/>
         <v>1888</v>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <f t="shared" si="13"/>
         <v>1889</v>
@@ -5100,7 +5100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <f t="shared" si="13"/>
         <v>1890</v>
@@ -5381,7 +5381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <f t="shared" si="13"/>
         <v>1891</v>
@@ -5662,7 +5662,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="64" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <f t="shared" si="13"/>
         <v>1892</v>
@@ -5943,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <f t="shared" si="13"/>
         <v>1893</v>
@@ -6224,7 +6224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <f t="shared" si="13"/>
         <v>1894</v>
@@ -6505,7 +6505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <f>A68-1</f>
         <v>1895</v>
@@ -6786,7 +6786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>1896</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <f>A68+1</f>
         <v>1897</v>
@@ -7347,7 +7347,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <f t="shared" ref="A70:A87" si="67">A69+1</f>
         <v>1898</v>
@@ -7628,7 +7628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <f t="shared" si="67"/>
         <v>1899</v>
@@ -7909,7 +7909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <f t="shared" si="67"/>
         <v>1900</v>
@@ -8190,7 +8190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <f t="shared" si="67"/>
         <v>1901</v>
@@ -8471,7 +8471,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="74" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <f t="shared" si="67"/>
         <v>1902</v>
@@ -8752,7 +8752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <f t="shared" si="67"/>
         <v>1903</v>
@@ -9033,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <f t="shared" si="67"/>
         <v>1904</v>
@@ -9314,7 +9314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <f t="shared" si="67"/>
         <v>1905</v>
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <f t="shared" si="67"/>
         <v>1906</v>
@@ -9876,7 +9876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <f t="shared" si="67"/>
         <v>1907</v>
@@ -10157,7 +10157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <f t="shared" si="67"/>
         <v>1908</v>
@@ -10438,7 +10438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <f t="shared" si="67"/>
         <v>1909</v>
@@ -10719,7 +10719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <f t="shared" si="67"/>
         <v>1910</v>
@@ -11000,7 +11000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <f t="shared" si="67"/>
         <v>1911</v>
@@ -11281,7 +11281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <f t="shared" si="67"/>
         <v>1912</v>
@@ -11562,7 +11562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <f t="shared" si="67"/>
         <v>1913</v>
@@ -11843,7 +11843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <f t="shared" si="67"/>
         <v>1914</v>
@@ -12124,7 +12124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <f t="shared" si="67"/>
         <v>1915</v>
@@ -12405,7 +12405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>50</v>
       </c>
@@ -12567,7 +12567,7 @@
       <c r="CE88" s="1"/>
       <c r="CF88" s="1"/>
     </row>
-    <row r="89" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>4</v>
       </c>
@@ -12722,7 +12722,7 @@
       <c r="BW89" s="1"/>
       <c r="BX89" s="1"/>
     </row>
-    <row r="90" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>51</v>
       </c>
@@ -12877,13 +12877,13 @@
       <c r="BW90" s="1"/>
       <c r="BX90" s="1"/>
     </row>
-    <row r="91" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:84" x14ac:dyDescent="0.25">
       <c r="AS91" s="1"/>
       <c r="AT91" s="1"/>
       <c r="BK91" s="1"/>
       <c r="BL91" s="1"/>
     </row>
-    <row r="92" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>58</v>
       </c>
@@ -12892,13 +12892,13 @@
       <c r="BK92" s="1"/>
       <c r="BL92" s="1"/>
     </row>
-    <row r="93" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:84" x14ac:dyDescent="0.25">
       <c r="AS93" s="1"/>
       <c r="AT93" s="1"/>
       <c r="BK93" s="1"/>
       <c r="BL93" s="1"/>
     </row>
-    <row r="94" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>59</v>
       </c>
@@ -12907,11 +12907,11 @@
       <c r="BK94" s="1"/>
       <c r="BL94" s="1"/>
     </row>
-    <row r="95" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:84" x14ac:dyDescent="0.25">
       <c r="BK95" s="1"/>
       <c r="BL95" s="1"/>
     </row>
-    <row r="96" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:84" x14ac:dyDescent="0.25">
       <c r="B96" s="16" t="s">
         <v>50</v>
       </c>
@@ -12924,7 +12924,7 @@
       <c r="BK96" s="1"/>
       <c r="BL96" s="1"/>
     </row>
-    <row r="97" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>7</v>
       </c>
@@ -12940,7 +12940,7 @@
       <c r="BK97" s="1"/>
       <c r="BL97" s="1"/>
     </row>
-    <row r="98" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -12956,7 +12956,7 @@
       <c r="BK98" s="1"/>
       <c r="BL98" s="1"/>
     </row>
-    <row r="99" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>21</v>
       </c>
@@ -12972,7 +12972,7 @@
       <c r="BK99" s="1"/>
       <c r="BL99" s="1"/>
     </row>
-    <row r="100" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>22</v>
       </c>
@@ -12988,7 +12988,7 @@
       <c r="BK100" s="1"/>
       <c r="BL100" s="1"/>
     </row>
-    <row r="101" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -13004,7 +13004,7 @@
       <c r="BK101" s="1"/>
       <c r="BL101" s="1"/>
     </row>
-    <row r="102" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>24</v>
       </c>
@@ -13020,7 +13020,7 @@
       <c r="BK102" s="1"/>
       <c r="BL102" s="1"/>
     </row>
-    <row r="103" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>25</v>
       </c>
@@ -13036,7 +13036,7 @@
       <c r="BK103" s="1"/>
       <c r="BL103" s="1"/>
     </row>
-    <row r="104" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>26</v>
       </c>
@@ -13052,7 +13052,7 @@
       <c r="BK104" s="1"/>
       <c r="BL104" s="1"/>
     </row>
-    <row r="105" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>27</v>
       </c>
@@ -13068,7 +13068,7 @@
       <c r="BK105" s="1"/>
       <c r="BL105" s="1"/>
     </row>
-    <row r="106" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>28</v>
       </c>
@@ -13084,7 +13084,7 @@
       <c r="BK106" s="1"/>
       <c r="BL106" s="1"/>
     </row>
-    <row r="107" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>9</v>
       </c>
@@ -13100,7 +13100,7 @@
       <c r="BK107" s="1"/>
       <c r="BL107" s="1"/>
     </row>
-    <row r="108" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>29</v>
       </c>
@@ -13116,7 +13116,7 @@
       <c r="BK108" s="1"/>
       <c r="BL108" s="1"/>
     </row>
-    <row r="109" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>30</v>
       </c>
@@ -13130,7 +13130,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="110" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>31</v>
       </c>
@@ -13144,7 +13144,7 @@
         <v>10183</v>
       </c>
     </row>
-    <row r="111" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>32</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="112" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>33</v>
       </c>
@@ -13172,7 +13172,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>34</v>
       </c>
@@ -13186,7 +13186,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>35</v>
       </c>
@@ -13200,7 +13200,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>12</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>501957</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -13228,7 +13228,7 @@
         <v>203217</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>36</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>254645</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>37</v>
       </c>
@@ -13256,7 +13256,7 @@
         <v>17031</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>53</v>
       </c>
@@ -13270,7 +13270,7 @@
         <v>-7316</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>38</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v>27485</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>54</v>
       </c>
@@ -13298,17 +13298,17 @@
         <v>1648192</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B126" s="16" t="s">
         <v>50</v>
       </c>
@@ -13323,7 +13323,7 @@
       <c r="M126" s="12"/>
       <c r="N126" s="12"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -13341,7 +13341,7 @@
       <c r="M127" s="11"/>
       <c r="N127" s="11"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -13359,7 +13359,7 @@
       <c r="M128" s="11"/>
       <c r="N128" s="11"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -13377,7 +13377,7 @@
       <c r="M129" s="11"/>
       <c r="N129" s="11"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>12</v>
       </c>
@@ -13395,7 +13395,7 @@
       <c r="M130" s="11"/>
       <c r="N130" s="11"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -13413,7 +13413,7 @@
       <c r="M131" s="11"/>
       <c r="N131" s="11"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>11</v>
       </c>
@@ -13431,7 +13431,7 @@
       <c r="M132" s="11"/>
       <c r="N132" s="11"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>54</v>
       </c>
@@ -13448,22 +13448,22 @@
         <v>932892</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B138" s="16" t="s">
         <v>50</v>
       </c>
@@ -13474,7 +13474,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>7</v>
       </c>
@@ -13491,7 +13491,7 @@
         <v>771797</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>8</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>418748</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>21</v>
       </c>
@@ -13525,7 +13525,7 @@
         <v>13736</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>22</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>28070</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>23</v>
       </c>
@@ -13559,7 +13559,7 @@
         <v>12366</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>24</v>
       </c>
@@ -13576,7 +13576,7 @@
         <v>3156</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>25</v>
       </c>
@@ -13593,7 +13593,7 @@
         <v>10838</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>26</v>
       </c>
@@ -13610,7 +13610,7 @@
         <v>5850</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>27</v>
       </c>
@@ -13627,7 +13627,7 @@
         <v>10344</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>28</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>9593</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>9</v>
       </c>
@@ -13661,7 +13661,7 @@
         <v>19318</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>29</v>
       </c>
@@ -13678,7 +13678,7 @@
         <v>10753</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>30</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>31</v>
       </c>
@@ -13712,7 +13712,7 @@
         <v>10183</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>32</v>
       </c>
@@ -13729,7 +13729,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>33</v>
       </c>
@@ -13746,7 +13746,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>34</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>35</v>
       </c>
@@ -13780,7 +13780,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>12</v>
       </c>
@@ -13797,7 +13797,7 @@
         <v>653207</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>10</v>
       </c>
@@ -13814,7 +13814,7 @@
         <v>292727</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>36</v>
       </c>
@@ -13831,7 +13831,7 @@
         <v>254645</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>37</v>
       </c>
@@ -13848,7 +13848,7 @@
         <v>17031</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>53</v>
       </c>
@@ -13865,7 +13865,7 @@
         <v>-7316</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>38</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>38605</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>54</v>
       </c>
@@ -13913,33 +13913,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C7873D5-0E5D-4C85-A503-F7801E4CF69A}">
   <dimension ref="A1:AE90"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11.68359375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="23" t="s">
         <v>5</v>
@@ -13957,7 +13957,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <f t="shared" ref="A9:A22" si="0">A10-1</f>
         <v>1881</v>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>1882</v>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>1883</v>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>1884</v>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>1885</v>
@@ -14185,7 +14185,7 @@
       </c>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>1886</v>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>1887</v>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>1888</v>
@@ -14302,7 +14302,7 @@
       </c>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <f t="shared" si="0"/>
         <v>1889</v>
@@ -14342,7 +14342,7 @@
       <c r="M17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <f t="shared" si="0"/>
         <v>1890</v>
@@ -14381,7 +14381,7 @@
       </c>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>1891</v>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>1892</v>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <f t="shared" si="0"/>
         <v>1893</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <f t="shared" si="0"/>
         <v>1894</v>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <f>A24-1</f>
         <v>1895</v>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>1896</v>
       </c>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <f>A24+1</f>
         <v>1897</v>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <f t="shared" ref="A26:A43" si="12">A25+1</f>
         <v>1898</v>
@@ -14692,7 +14692,7 @@
       </c>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <f t="shared" si="12"/>
         <v>1899</v>
@@ -14731,7 +14731,7 @@
       </c>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <f t="shared" si="12"/>
         <v>1900</v>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <f t="shared" si="12"/>
         <v>1901</v>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <f t="shared" si="12"/>
         <v>1902</v>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <f t="shared" si="12"/>
         <v>1903</v>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <f t="shared" si="12"/>
         <v>1904</v>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <f t="shared" si="12"/>
         <v>1905</v>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <f t="shared" si="12"/>
         <v>1906</v>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <f t="shared" si="12"/>
         <v>1907</v>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <f t="shared" si="12"/>
         <v>1908</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <f t="shared" si="12"/>
         <v>1909</v>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <f t="shared" si="12"/>
         <v>1910</v>
@@ -15160,7 +15160,7 @@
       </c>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <f t="shared" si="12"/>
         <v>1911</v>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <f t="shared" si="12"/>
         <v>1912</v>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <f t="shared" si="12"/>
         <v>1913</v>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <f t="shared" si="12"/>
         <v>1914</v>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <f t="shared" si="12"/>
         <v>1915</v>
@@ -15355,7 +15355,7 @@
       </c>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>50</v>
       </c>
@@ -15379,7 +15379,7 @@
       <c r="J44" s="5"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>4</v>
       </c>
@@ -15403,7 +15403,7 @@
       <c r="J45" s="4"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>51</v>
       </c>
@@ -15427,25 +15427,25 @@
       <c r="J46" s="4"/>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>60</v>
       </c>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
       <c r="O50" s="1"/>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="23" t="s">
         <v>7</v>
@@ -15487,7 +15487,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>0</v>
       </c>
@@ -15573,7 +15573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <f t="shared" ref="A53:A66" si="13">A54-1</f>
         <v>1881</v>
@@ -15665,7 +15665,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <f t="shared" si="13"/>
         <v>1882</v>
@@ -15751,7 +15751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <f t="shared" si="13"/>
         <v>1883</v>
@@ -15831,7 +15831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <f t="shared" si="13"/>
         <v>1884</v>
@@ -15917,7 +15917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <f t="shared" si="13"/>
         <v>1885</v>
@@ -15997,7 +15997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <f t="shared" si="13"/>
         <v>1886</v>
@@ -16083,7 +16083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <f t="shared" si="13"/>
         <v>1887</v>
@@ -16162,7 +16162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <f t="shared" si="13"/>
         <v>1888</v>
@@ -16241,7 +16241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <f t="shared" si="13"/>
         <v>1889</v>
@@ -16275,7 +16275,7 @@
         <v>978790</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <f t="shared" si="13"/>
         <v>1890</v>
@@ -16309,7 +16309,7 @@
         <v>1335193</v>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <f t="shared" si="13"/>
         <v>1891</v>
@@ -16343,7 +16343,7 @@
         <v>1582858</v>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <f t="shared" si="13"/>
         <v>1892</v>
@@ -16377,7 +16377,7 @@
         <v>927302</v>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <f t="shared" si="13"/>
         <v>1893</v>
@@ -16411,7 +16411,7 @@
         <v>1057183</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <f t="shared" si="13"/>
         <v>1894</v>
@@ -16445,7 +16445,7 @@
         <v>933790</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <f>A68-1</f>
         <v>1895</v>
@@ -16479,7 +16479,7 @@
         <v>1485902</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>1896</v>
       </c>
@@ -16578,7 +16578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <f>A68+1</f>
         <v>1897</v>
@@ -16678,7 +16678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <f t="shared" ref="A70:A87" si="37">A69+1</f>
         <v>1898</v>
@@ -16778,7 +16778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <f t="shared" si="37"/>
         <v>1899</v>
@@ -16878,7 +16878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <f t="shared" si="37"/>
         <v>1900</v>
@@ -16978,7 +16978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <f t="shared" si="37"/>
         <v>1901</v>
@@ -17078,7 +17078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <f t="shared" si="37"/>
         <v>1902</v>
@@ -17178,7 +17178,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <f t="shared" si="37"/>
         <v>1903</v>
@@ -17278,7 +17278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <f t="shared" si="37"/>
         <v>1904</v>
@@ -17378,7 +17378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <f t="shared" si="37"/>
         <v>1905</v>
@@ -17478,7 +17478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <f t="shared" si="37"/>
         <v>1906</v>
@@ -17578,7 +17578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <f t="shared" si="37"/>
         <v>1907</v>
@@ -17678,7 +17678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <f t="shared" si="37"/>
         <v>1908</v>
@@ -17778,7 +17778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <f t="shared" si="37"/>
         <v>1909</v>
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <f t="shared" si="37"/>
         <v>1910</v>
@@ -17978,7 +17978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <f t="shared" si="37"/>
         <v>1911</v>
@@ -18078,7 +18078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <f t="shared" si="37"/>
         <v>1912</v>
@@ -18178,7 +18178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <f t="shared" si="37"/>
         <v>1913</v>
@@ -18278,7 +18278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <f t="shared" si="37"/>
         <v>1914</v>
@@ -18378,7 +18378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <f t="shared" si="37"/>
         <v>1915</v>
@@ -18476,7 +18476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>50</v>
       </c>
@@ -18523,7 +18523,7 @@
       <c r="V88" s="5"/>
       <c r="W88" s="5"/>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>4</v>
       </c>
@@ -18570,7 +18570,7 @@
       <c r="V89" s="4"/>
       <c r="W89" s="4"/>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>51</v>
       </c>
@@ -18637,43 +18637,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B60D45-40A7-4AEF-8152-6E6E2D19E14F}">
   <dimension ref="A1:AI93"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12.578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.26171875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.26171875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.26171875" customWidth="1"/>
-    <col min="13" max="13" width="11.578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.26171875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.68359375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.26171875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.41796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.68359375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.15625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.68359375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.68359375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.41796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.26171875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.41796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.68359375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.26171875" customWidth="1"/>
-    <col min="31" max="31" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.41796875" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" customWidth="1"/>
+    <col min="31" max="31" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -18768,7 +18768,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1881</v>
       </c>
@@ -18860,7 +18860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <f t="shared" ref="A3:A15" si="0">A4-1</f>
         <v>1882</v>
@@ -18950,7 +18950,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <f t="shared" si="0"/>
         <v>1883</v>
@@ -19040,7 +19040,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f t="shared" si="0"/>
         <v>1884</v>
@@ -19130,7 +19130,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <f t="shared" si="0"/>
         <v>1885</v>
@@ -19220,7 +19220,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>1886</v>
@@ -19310,7 +19310,7 @@
         <v>-297</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>1887</v>
@@ -19397,7 +19397,7 @@
         <v>-215</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>1888</v>
@@ -19484,7 +19484,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>1889</v>
@@ -19562,7 +19562,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>1890</v>
@@ -19640,7 +19640,7 @@
         <v>-706</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>1891</v>
@@ -19718,7 +19718,7 @@
         <v>-470</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>1892</v>
@@ -19796,7 +19796,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>1893</v>
@@ -19874,7 +19874,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>1894</v>
@@ -19952,7 +19952,7 @@
         <v>4552</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <f>A17-1</f>
         <v>1895</v>
@@ -20030,7 +20030,7 @@
         <v>4320</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>1896</v>
       </c>
@@ -20125,7 +20125,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <f>A17+1</f>
         <v>1897</v>
@@ -20221,7 +20221,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <f t="shared" ref="A19:A36" si="1">A18+1</f>
         <v>1898</v>
@@ -20317,7 +20317,7 @@
         <v>3325</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <f t="shared" si="1"/>
         <v>1899</v>
@@ -20413,7 +20413,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <f t="shared" si="1"/>
         <v>1900</v>
@@ -20509,7 +20509,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <f t="shared" si="1"/>
         <v>1901</v>
@@ -20605,7 +20605,7 @@
         <v>-1288</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <f t="shared" si="1"/>
         <v>1902</v>
@@ -20701,7 +20701,7 @@
         <v>-1670</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <f t="shared" si="1"/>
         <v>1903</v>
@@ -20797,7 +20797,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <f t="shared" si="1"/>
         <v>1904</v>
@@ -20893,7 +20893,7 @@
         <v>-2998</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <f t="shared" si="1"/>
         <v>1905</v>
@@ -20989,7 +20989,7 @@
         <v>-97</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <f t="shared" si="1"/>
         <v>1906</v>
@@ -21085,7 +21085,7 @@
         <v>3499</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <f t="shared" si="1"/>
         <v>1907</v>
@@ -21181,7 +21181,7 @@
         <v>9747</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <f t="shared" si="1"/>
         <v>1908</v>
@@ -21277,7 +21277,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <f t="shared" si="1"/>
         <v>1909</v>
@@ -21373,7 +21373,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <f t="shared" si="1"/>
         <v>1910</v>
@@ -21469,7 +21469,7 @@
         <v>-46</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <f t="shared" si="1"/>
         <v>1911</v>
@@ -21565,7 +21565,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <f t="shared" si="1"/>
         <v>1912</v>
@@ -21661,7 +21661,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <f t="shared" si="1"/>
         <v>1913</v>
@@ -21757,7 +21757,7 @@
         <v>-239</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <f t="shared" si="1"/>
         <v>1914</v>
@@ -21853,7 +21853,7 @@
         <v>-1287</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <f t="shared" si="1"/>
         <v>1915</v>
@@ -21949,13 +21949,13 @@
         <v>-2496</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>47</v>
       </c>
       <c r="P38" s="1"/>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
         <v>65</v>
       </c>
@@ -21973,22 +21973,22 @@
       <c r="M39" s="21"/>
       <c r="P39" s="1"/>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
         <v>41</v>
       </c>
@@ -22089,7 +22089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>50</v>
       </c>
@@ -22226,7 +22226,7 @@
         <v>368588</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>4</v>
       </c>
@@ -22363,7 +22363,7 @@
         <v>564304</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>51</v>
       </c>
@@ -22500,10 +22500,10 @@
         <v>932892</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" s="9"/>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>50</v>
       </c>
@@ -22608,7 +22608,7 @@
         <v>960967</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>4</v>
       </c>
@@ -22713,7 +22713,7 @@
         <v>1622024</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>51</v>
       </c>
@@ -22818,7 +22818,7 @@
         <v>2582991</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>1881</v>
       </c>
@@ -22924,7 +22924,7 @@
         <v>79013</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>1882</v>
       </c>
@@ -23030,7 +23030,7 @@
         <v>104178</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>1883</v>
       </c>
@@ -23136,7 +23136,7 @@
         <v>77501</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>1884</v>
       </c>
@@ -23242,7 +23242,7 @@
         <v>83035</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>1885</v>
       </c>
@@ -23348,7 +23348,7 @@
         <v>122521</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>1886</v>
       </c>
@@ -23454,7 +23454,7 @@
         <v>115732</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>1887</v>
       </c>
@@ -23560,7 +23560,7 @@
         <v>66315</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>1888</v>
       </c>
@@ -23666,7 +23666,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>1889</v>
       </c>
@@ -23772,7 +23772,7 @@
         <v>48891</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>1890</v>
       </c>
@@ -23878,7 +23878,7 @@
         <v>69548</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>1891</v>
       </c>
@@ -23928,7 +23928,7 @@
         <v>-275</v>
       </c>
       <c r="S65" s="1">
-        <f t="shared" ref="S65:Y74" si="23">S12</f>
+        <f t="shared" ref="S65:Y70" si="23">S12</f>
         <v>201</v>
       </c>
       <c r="T65" s="1">
@@ -23984,7 +23984,7 @@
         <v>20540</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>1892</v>
       </c>
@@ -24090,7 +24090,7 @@
         <v>29804</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>1893</v>
       </c>
@@ -24196,7 +24196,7 @@
         <v>52753</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>1894</v>
       </c>
@@ -24302,7 +24302,7 @@
         <v>34688</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>1895</v>
       </c>
@@ -24408,7 +24408,7 @@
         <v>-40452</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>1896</v>
       </c>
@@ -24514,7 +24514,7 @@
         <v>47701</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>1897</v>
       </c>
@@ -24620,7 +24620,7 @@
         <v>79397</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>1898</v>
       </c>
@@ -24726,7 +24726,7 @@
         <v>83642</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>1899</v>
       </c>
@@ -24832,7 +24832,7 @@
         <v>95154</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>1900</v>
       </c>
@@ -24938,7 +24938,7 @@
         <v>62552</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>1901</v>
       </c>
@@ -25043,7 +25043,7 @@
         <v>98598</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>1902</v>
       </c>
@@ -25149,7 +25149,7 @@
         <v>96037</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>1903</v>
       </c>
@@ -25254,7 +25254,7 @@
         <v>82100</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>1904</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>54675</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>1905</v>
       </c>
@@ -25464,7 +25464,7 @@
         <v>9066</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>1906</v>
       </c>
@@ -25569,7 +25569,7 @@
         <v>20407</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>1907</v>
       </c>
@@ -25674,7 +25674,7 @@
         <v>103322</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>1908</v>
       </c>
@@ -25779,7 +25779,7 @@
         <v>82309</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>1909</v>
       </c>
@@ -25884,7 +25884,7 @@
         <v>110099</v>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>1910</v>
       </c>
@@ -25989,7 +25989,7 @@
         <v>53529</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>1911</v>
       </c>
@@ -26002,7 +26002,7 @@
         <v>14467</v>
       </c>
       <c r="J85" s="1">
-        <f t="shared" ref="J85:Q94" si="26">J32</f>
+        <f t="shared" ref="J85:Q86" si="26">J32</f>
         <v>885</v>
       </c>
       <c r="K85" s="1">
@@ -26094,7 +26094,7 @@
         <v>93656</v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>1912</v>
       </c>
@@ -26199,7 +26199,7 @@
         <v>114673</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>1913</v>
       </c>
@@ -26304,7 +26304,7 @@
         <v>186204</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>1914</v>
       </c>
@@ -26409,7 +26409,7 @@
         <v>99625</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>1915</v>
       </c>
@@ -26514,19 +26514,19 @@
         <v>49278</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AG91" s="1">
         <f>SUM(AG55:AG69)</f>
         <v>960967</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AG92" s="1">
         <f>SUM(AG70:AG89)</f>
         <v>1622024</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AG93" s="1">
         <f>AG92+AG91</f>
         <v>2582991</v>
@@ -26541,42 +26541,42 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE18E4D5-6DC9-4566-AC84-244F24C82204}">
   <dimension ref="A1:AI93"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.68359375" customWidth="1"/>
-    <col min="2" max="2" width="11.62890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.05078125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.26171875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.20703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.15625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.15625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.3671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.15625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.62890625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.9453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.89453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.62890625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.7890625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.1015625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.05078125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.9453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.47265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="7.15625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.5234375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.05078125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.62890625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.15625" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -26671,7 +26671,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1881</v>
       </c>
@@ -26763,7 +26763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <f t="shared" ref="A3:A15" si="0">A4-1</f>
         <v>1882</v>
@@ -26853,7 +26853,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <f t="shared" si="0"/>
         <v>1883</v>
@@ -26943,7 +26943,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f t="shared" si="0"/>
         <v>1884</v>
@@ -27033,7 +27033,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <f t="shared" si="0"/>
         <v>1885</v>
@@ -27123,7 +27123,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>1886</v>
@@ -27213,7 +27213,7 @@
         <v>-297</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>1887</v>
@@ -27300,7 +27300,7 @@
         <v>-215</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>1888</v>
@@ -27387,7 +27387,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>1889</v>
@@ -27465,7 +27465,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>1890</v>
@@ -27543,7 +27543,7 @@
         <v>-706</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>1891</v>
@@ -27621,7 +27621,7 @@
         <v>-470</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>1892</v>
@@ -27699,7 +27699,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>1893</v>
@@ -27777,7 +27777,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>1894</v>
@@ -27855,7 +27855,7 @@
         <v>4552</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <f>A17-1</f>
         <v>1895</v>
@@ -27934,7 +27934,7 @@
         <v>4320</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>1896</v>
       </c>
@@ -28029,7 +28029,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <f>A17+1</f>
         <v>1897</v>
@@ -28125,7 +28125,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <f t="shared" ref="A19:A36" si="1">A18+1</f>
         <v>1898</v>
@@ -28221,7 +28221,7 @@
         <v>3325</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <f t="shared" si="1"/>
         <v>1899</v>
@@ -28317,7 +28317,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <f t="shared" si="1"/>
         <v>1900</v>
@@ -28413,7 +28413,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <f t="shared" si="1"/>
         <v>1901</v>
@@ -28509,7 +28509,7 @@
         <v>-1288</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <f t="shared" si="1"/>
         <v>1902</v>
@@ -28605,7 +28605,7 @@
         <v>-1670</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <f t="shared" si="1"/>
         <v>1903</v>
@@ -28701,7 +28701,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <f t="shared" si="1"/>
         <v>1904</v>
@@ -28797,7 +28797,7 @@
         <v>-2998</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <f t="shared" si="1"/>
         <v>1905</v>
@@ -28893,7 +28893,7 @@
         <v>-97</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <f t="shared" si="1"/>
         <v>1906</v>
@@ -28990,7 +28990,7 @@
         <v>3499</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <f t="shared" si="1"/>
         <v>1907</v>
@@ -29086,7 +29086,7 @@
         <v>9747</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <f t="shared" si="1"/>
         <v>1908</v>
@@ -29182,7 +29182,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <f t="shared" si="1"/>
         <v>1909</v>
@@ -29278,7 +29278,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <f t="shared" si="1"/>
         <v>1910</v>
@@ -29375,7 +29375,7 @@
         <v>-46</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <f t="shared" si="1"/>
         <v>1911</v>
@@ -29471,7 +29471,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <f t="shared" si="1"/>
         <v>1912</v>
@@ -29567,7 +29567,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <f t="shared" si="1"/>
         <v>1913</v>
@@ -29663,7 +29663,7 @@
         <v>-239</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <f t="shared" si="1"/>
         <v>1914</v>
@@ -29759,7 +29759,7 @@
         <v>-1287</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <f t="shared" si="1"/>
         <v>1915</v>
@@ -29855,13 +29855,13 @@
         <v>-2496</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>47</v>
       </c>
       <c r="P38" s="1"/>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
         <v>69</v>
       </c>
@@ -29879,22 +29879,22 @@
       <c r="M39" s="21"/>
       <c r="P39" s="1"/>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
         <v>41</v>
       </c>
@@ -29995,7 +29995,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>50</v>
       </c>
@@ -30132,7 +30132,7 @@
         <v>368588</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>4</v>
       </c>
@@ -30269,7 +30269,7 @@
         <v>674304</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>51</v>
       </c>
@@ -30406,10 +30406,10 @@
         <v>1042892</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" s="9"/>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>50</v>
       </c>
@@ -30514,7 +30514,7 @@
         <v>1060967</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>4</v>
       </c>
@@ -30619,7 +30619,7 @@
         <v>1732024</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>51</v>
       </c>
@@ -30724,7 +30724,7 @@
         <v>2792991</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>1881</v>
       </c>
@@ -30830,7 +30830,7 @@
         <v>79013</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>1882</v>
       </c>
@@ -30936,7 +30936,7 @@
         <v>104178</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>1883</v>
       </c>
@@ -31042,7 +31042,7 @@
         <v>77501</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>1884</v>
       </c>
@@ -31148,7 +31148,7 @@
         <v>83035</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>1885</v>
       </c>
@@ -31254,7 +31254,7 @@
         <v>122521</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>1886</v>
       </c>
@@ -31360,7 +31360,7 @@
         <v>115732</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>1887</v>
       </c>
@@ -31466,7 +31466,7 @@
         <v>66315</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>1888</v>
       </c>
@@ -31572,7 +31572,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>1889</v>
       </c>
@@ -31678,7 +31678,7 @@
         <v>48891</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>1890</v>
       </c>
@@ -31784,7 +31784,7 @@
         <v>69548</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>1891</v>
       </c>
@@ -31834,7 +31834,7 @@
         <v>-275</v>
       </c>
       <c r="S65" s="1">
-        <f t="shared" ref="S65:Y74" si="21">S12</f>
+        <f t="shared" ref="S65:Y70" si="21">S12</f>
         <v>201</v>
       </c>
       <c r="T65" s="1">
@@ -31890,7 +31890,7 @@
         <v>20540</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>1892</v>
       </c>
@@ -31996,7 +31996,7 @@
         <v>29804</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>1893</v>
       </c>
@@ -32102,7 +32102,7 @@
         <v>52753</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>1894</v>
       </c>
@@ -32208,7 +32208,7 @@
         <v>34688</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>1895</v>
       </c>
@@ -32314,7 +32314,7 @@
         <v>59548</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>1896</v>
       </c>
@@ -32420,7 +32420,7 @@
         <v>47701</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>1897</v>
       </c>
@@ -32526,7 +32526,7 @@
         <v>79397</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>1898</v>
       </c>
@@ -32632,7 +32632,7 @@
         <v>83642</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>1899</v>
       </c>
@@ -32738,7 +32738,7 @@
         <v>95154</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>1900</v>
       </c>
@@ -32844,7 +32844,7 @@
         <v>62552</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>1901</v>
       </c>
@@ -32949,7 +32949,7 @@
         <v>98598</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>1902</v>
       </c>
@@ -33055,7 +33055,7 @@
         <v>96037</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>1903</v>
       </c>
@@ -33160,7 +33160,7 @@
         <v>82100</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>1904</v>
       </c>
@@ -33265,7 +33265,7 @@
         <v>54675</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>1905</v>
       </c>
@@ -33370,7 +33370,7 @@
         <v>9066</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>1906</v>
       </c>
@@ -33475,7 +33475,7 @@
         <v>70407</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>1907</v>
       </c>
@@ -33580,7 +33580,7 @@
         <v>103322</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>1908</v>
       </c>
@@ -33685,7 +33685,7 @@
         <v>82309</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>1909</v>
       </c>
@@ -33790,7 +33790,7 @@
         <v>110099</v>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>1910</v>
       </c>
@@ -33895,7 +33895,7 @@
         <v>113529</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>1911</v>
       </c>
@@ -33908,7 +33908,7 @@
         <v>14467</v>
       </c>
       <c r="J85" s="1">
-        <f t="shared" ref="J85:Q94" si="24">J32</f>
+        <f t="shared" ref="J85:Q86" si="24">J32</f>
         <v>885</v>
       </c>
       <c r="K85" s="1">
@@ -34000,7 +34000,7 @@
         <v>93656</v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>1912</v>
       </c>
@@ -34105,7 +34105,7 @@
         <v>114673</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>1913</v>
       </c>
@@ -34210,7 +34210,7 @@
         <v>186204</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>1914</v>
       </c>
@@ -34315,7 +34315,7 @@
         <v>99625</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>1915</v>
       </c>
@@ -34420,19 +34420,19 @@
         <v>49278</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AG91" s="1">
         <f>SUM(AG55:AG69)</f>
         <v>1060967</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AG92" s="1">
         <f>SUM(AG70:AG89)</f>
         <v>1732024</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AG93" s="1">
         <f>AG92+AG91</f>
         <v>2792991</v>
